--- a/FPE/Outputs/cruces_p21_p22_genero_ocupacion.xlsx
+++ b/FPE/Outputs/cruces_p21_p22_genero_ocupacion.xlsx
@@ -8,22 +8,41 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/FPE/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F3756512CD25B7C54497507D7B70B2602336ABA1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{810B1BDB-BAC9-41F3-A30A-B07D48F2B923}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_1272E19AAE737EC6EF8CFB722C348F54C2BA38D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84858570-7F4B-4410-BC27-74F8851CCFFE}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6456" yWindow="4056" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="p22_x_genero" sheetId="1" r:id="rId1"/>
     <sheet name="p22_x_genero_x_p7" sheetId="2" r:id="rId2"/>
     <sheet name="p22_x_genero_x_p7_agregado" sheetId="3" r:id="rId3"/>
     <sheet name="p21_x_genero" sheetId="4" r:id="rId4"/>
+    <sheet name="p21_x_genero_x_p23_x_edad" sheetId="5" r:id="rId5"/>
+    <sheet name="Hoja1" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">p21_x_genero_x_p23_x_edad!$A$1:$G$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">p22_x_genero_x_p7!$A$1:$F$115</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="61">
   <si>
     <t>ciudad</t>
   </si>
@@ -144,6 +163,69 @@
   <si>
     <t>Uno</t>
   </si>
+  <si>
+    <t>p23_agregado</t>
+  </si>
+  <si>
+    <t>edad_r2</t>
+  </si>
+  <si>
+    <t>Estudio</t>
+  </si>
+  <si>
+    <t>18 - 34 años</t>
+  </si>
+  <si>
+    <t>35 - 54 años</t>
+  </si>
+  <si>
+    <t>55 - 80 años</t>
+  </si>
+  <si>
+    <t>Recreación y actividades personales</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Trabajo</t>
+  </si>
+  <si>
+    <t>Trámites</t>
+  </si>
+  <si>
+    <t>Viajes de cuidado</t>
+  </si>
+  <si>
+    <t>Visitas sociales</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>HM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres Cali </t>
+  </si>
+  <si>
+    <t>Número de destinos durante el viaje (viajes de cuidado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujeres Cali </t>
+  </si>
+  <si>
+    <t>Hombres Medellín</t>
+  </si>
+  <si>
+    <t>Mujeres Medellín</t>
+  </si>
 </sst>
 </file>
 
@@ -194,12 +276,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -216,6 +307,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,9 +602,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -541,7 +633,7 @@
       <c r="D2">
         <v>37</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>0.17452830188679239</v>
       </c>
     </row>
@@ -558,7 +650,7 @@
       <c r="D3">
         <v>50</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>0.23584905660377359</v>
       </c>
     </row>
@@ -575,7 +667,7 @@
       <c r="D4">
         <v>54</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>0.25471698113207553</v>
       </c>
     </row>
@@ -592,7 +684,7 @@
       <c r="D5">
         <v>17</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>8.0188679245283015E-2</v>
       </c>
     </row>
@@ -609,7 +701,7 @@
       <c r="D6">
         <v>54</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>0.25471698113207553</v>
       </c>
     </row>
@@ -626,7 +718,7 @@
       <c r="D7">
         <v>61</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>0.27601809954751128</v>
       </c>
     </row>
@@ -643,7 +735,7 @@
       <c r="D8">
         <v>43</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>0.19457013574660631</v>
       </c>
     </row>
@@ -660,7 +752,7 @@
       <c r="D9">
         <v>37</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
         <v>0.167420814479638</v>
       </c>
     </row>
@@ -677,7 +769,7 @@
       <c r="D10">
         <v>41</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10">
         <v>0.18552036199095021</v>
       </c>
     </row>
@@ -694,7 +786,7 @@
       <c r="D11">
         <v>39</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11">
         <v>0.1764705882352941</v>
       </c>
     </row>
@@ -711,7 +803,7 @@
       <c r="D12">
         <v>31</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>0.16489361702127661</v>
       </c>
     </row>
@@ -728,7 +820,7 @@
       <c r="D13">
         <v>21</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13">
         <v>0.1117021276595745</v>
       </c>
     </row>
@@ -745,7 +837,7 @@
       <c r="D14">
         <v>58</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14">
         <v>0.30851063829787229</v>
       </c>
     </row>
@@ -762,7 +854,7 @@
       <c r="D15">
         <v>64</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15">
         <v>0.34042553191489361</v>
       </c>
     </row>
@@ -779,7 +871,7 @@
       <c r="D16">
         <v>14</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16">
         <v>7.4468085106382975E-2</v>
       </c>
     </row>
@@ -796,7 +888,7 @@
       <c r="D17">
         <v>35</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
         <v>0.16666666666666671</v>
       </c>
     </row>
@@ -813,7 +905,7 @@
       <c r="D18">
         <v>19</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18">
         <v>9.0476190476190474E-2</v>
       </c>
     </row>
@@ -830,7 +922,7 @@
       <c r="D19">
         <v>51</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19">
         <v>0.24285714285714291</v>
       </c>
     </row>
@@ -847,7 +939,7 @@
       <c r="D20">
         <v>85</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20">
         <v>0.40476190476190482</v>
       </c>
     </row>
@@ -864,7 +956,7 @@
       <c r="D21">
         <v>20</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21">
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
@@ -877,6 +969,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="37.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3179,6 +3274,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F115" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4697,9 +4793,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="28.88671875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -4731,7 +4824,7 @@
       <c r="D2">
         <v>39</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>0.18396226415094341</v>
       </c>
     </row>
@@ -4748,7 +4841,7 @@
       <c r="D3">
         <v>66</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>0.31132075471698112</v>
       </c>
     </row>
@@ -4765,7 +4858,7 @@
       <c r="D4">
         <v>16</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>7.5471698113207544E-2</v>
       </c>
     </row>
@@ -4782,7 +4875,7 @@
       <c r="D5">
         <v>35</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>0.1650943396226415</v>
       </c>
     </row>
@@ -4799,7 +4892,7 @@
       <c r="D6">
         <v>56</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>0.26415094339622641</v>
       </c>
     </row>
@@ -4816,7 +4909,7 @@
       <c r="D7">
         <v>10</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>4.5248868778280542E-2</v>
       </c>
     </row>
@@ -4833,7 +4926,7 @@
       <c r="D8">
         <v>60</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>0.27149321266968318</v>
       </c>
     </row>
@@ -4850,7 +4943,7 @@
       <c r="D9">
         <v>38</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
         <v>0.17194570135746609</v>
       </c>
     </row>
@@ -4867,7 +4960,7 @@
       <c r="D10">
         <v>25</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10">
         <v>0.1131221719457014</v>
       </c>
     </row>
@@ -4884,7 +4977,7 @@
       <c r="D11">
         <v>88</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11">
         <v>0.39819004524886881</v>
       </c>
     </row>
@@ -4901,7 +4994,7 @@
       <c r="D12">
         <v>15</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>7.9787234042553196E-2</v>
       </c>
     </row>
@@ -4918,7 +5011,7 @@
       <c r="D13">
         <v>49</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13">
         <v>0.26063829787234039</v>
       </c>
     </row>
@@ -4935,7 +5028,7 @@
       <c r="D14">
         <v>9</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14">
         <v>4.7872340425531908E-2</v>
       </c>
     </row>
@@ -4952,7 +5045,7 @@
       <c r="D15">
         <v>23</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15">
         <v>0.1223404255319149</v>
       </c>
     </row>
@@ -4969,7 +5062,7 @@
       <c r="D16">
         <v>92</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16">
         <v>0.48936170212765961</v>
       </c>
     </row>
@@ -4986,7 +5079,7 @@
       <c r="D17">
         <v>13</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
         <v>6.1904761904761907E-2</v>
       </c>
     </row>
@@ -5003,7 +5096,7 @@
       <c r="D18">
         <v>47</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18">
         <v>0.22380952380952379</v>
       </c>
     </row>
@@ -5020,7 +5113,7 @@
       <c r="D19">
         <v>34</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19">
         <v>0.16190476190476191</v>
       </c>
     </row>
@@ -5037,7 +5130,7 @@
       <c r="D20">
         <v>11</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20">
         <v>5.2380952380952382E-2</v>
       </c>
     </row>
@@ -5054,11 +5147,5604 @@
       <c r="D21">
         <v>105</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G238"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0.1818181818181818</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>0.63636363636363635</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" t="s">
+        <v>35</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>0.27777777777777779</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>3.8461538461538457E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53">
+        <v>9</v>
+      </c>
+      <c r="G53">
+        <v>0.34615384615384609</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>7.6923076923076927E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+      <c r="G55">
+        <v>0.30769230769230771</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57">
+        <v>21</v>
+      </c>
+      <c r="G57">
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>2.222222222222222E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" t="s">
+        <v>39</v>
+      </c>
+      <c r="F60">
+        <v>12</v>
+      </c>
+      <c r="G60">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61">
+        <v>4.6511627906976737E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62">
+        <v>16</v>
+      </c>
+      <c r="G62">
+        <v>0.37209302325581389</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" t="s">
+        <v>37</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>4.6511627906976737E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64">
+        <v>0.1162790697674419</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>48</v>
+      </c>
+      <c r="D65" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65" t="s">
+        <v>39</v>
+      </c>
+      <c r="F65">
+        <v>18</v>
+      </c>
+      <c r="G65">
+        <v>0.41860465116279072</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>48</v>
+      </c>
+      <c r="D66" t="s">
+        <v>44</v>
+      </c>
+      <c r="E66" t="s">
+        <v>35</v>
+      </c>
+      <c r="F66">
+        <v>14</v>
+      </c>
+      <c r="G66">
+        <v>0.25925925925925919</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" t="s">
+        <v>44</v>
+      </c>
+      <c r="E67" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67">
+        <v>19</v>
+      </c>
+      <c r="G67">
+        <v>0.35185185185185192</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" t="s">
+        <v>44</v>
+      </c>
+      <c r="E68" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68">
+        <v>5.5555555555555552E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" t="s">
+        <v>44</v>
+      </c>
+      <c r="E69" t="s">
+        <v>38</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="G69">
+        <v>0.14814814814814811</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>48</v>
+      </c>
+      <c r="D70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E70" t="s">
+        <v>39</v>
+      </c>
+      <c r="F70">
+        <v>10</v>
+      </c>
+      <c r="G70">
+        <v>0.1851851851851852</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" t="s">
+        <v>44</v>
+      </c>
+      <c r="E71" t="s">
+        <v>35</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71">
+        <v>6.1224489795918373E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" t="s">
+        <v>44</v>
+      </c>
+      <c r="E72" t="s">
+        <v>36</v>
+      </c>
+      <c r="F72">
+        <v>10</v>
+      </c>
+      <c r="G72">
+        <v>0.2040816326530612</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>48</v>
+      </c>
+      <c r="D73" t="s">
+        <v>44</v>
+      </c>
+      <c r="E73" t="s">
+        <v>37</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73">
+        <v>0.16326530612244899</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" t="s">
+        <v>44</v>
+      </c>
+      <c r="E74" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74">
+        <v>7</v>
+      </c>
+      <c r="G74">
+        <v>0.14285714285714279</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" t="s">
+        <v>44</v>
+      </c>
+      <c r="E75" t="s">
+        <v>39</v>
+      </c>
+      <c r="F75">
+        <v>21</v>
+      </c>
+      <c r="G75">
+        <v>0.42857142857142849</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s">
+        <v>48</v>
+      </c>
+      <c r="D76" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" t="s">
+        <v>35</v>
+      </c>
+      <c r="F76">
+        <v>8</v>
+      </c>
+      <c r="G76">
+        <v>0.2162162162162162</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" t="s">
+        <v>36</v>
+      </c>
+      <c r="F77">
+        <v>6</v>
+      </c>
+      <c r="G77">
+        <v>0.1621621621621622</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="G78">
+        <v>0.13513513513513509</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79">
+        <v>0.2162162162162162</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" t="s">
+        <v>39</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80">
+        <v>0.27027027027027029</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>48</v>
+      </c>
+      <c r="D81" t="s">
+        <v>45</v>
+      </c>
+      <c r="E81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" t="s">
+        <v>45</v>
+      </c>
+      <c r="E82" t="s">
+        <v>36</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" t="s">
+        <v>45</v>
+      </c>
+      <c r="E84" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84">
+        <v>4</v>
+      </c>
+      <c r="G84">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85" t="s">
+        <v>45</v>
+      </c>
+      <c r="E85" t="s">
+        <v>39</v>
+      </c>
+      <c r="F85">
+        <v>4</v>
+      </c>
+      <c r="G85">
+        <v>0.26666666666666672</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" t="s">
+        <v>43</v>
+      </c>
+      <c r="E86" t="s">
+        <v>38</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87" t="s">
+        <v>43</v>
+      </c>
+      <c r="E87" t="s">
+        <v>37</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>49</v>
+      </c>
+      <c r="D88" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>49</v>
+      </c>
+      <c r="D89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" t="s">
+        <v>35</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>49</v>
+      </c>
+      <c r="D90" t="s">
+        <v>44</v>
+      </c>
+      <c r="E90" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
+        <v>49</v>
+      </c>
+      <c r="D91" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" t="s">
+        <v>49</v>
+      </c>
+      <c r="D94" t="s">
+        <v>44</v>
+      </c>
+      <c r="E94" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" t="s">
+        <v>45</v>
+      </c>
+      <c r="E95" t="s">
+        <v>35</v>
+      </c>
+      <c r="F95">
+        <v>2</v>
+      </c>
+      <c r="G95">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>49</v>
+      </c>
+      <c r="D96" t="s">
+        <v>45</v>
+      </c>
+      <c r="E96" t="s">
+        <v>39</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" t="s">
+        <v>49</v>
+      </c>
+      <c r="D97" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" t="s">
+        <v>36</v>
+      </c>
+      <c r="F97">
+        <v>2</v>
+      </c>
+      <c r="G97">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" t="s">
+        <v>37</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>49</v>
+      </c>
+      <c r="D99" t="s">
+        <v>45</v>
+      </c>
+      <c r="E99" t="s">
+        <v>39</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" t="s">
+        <v>50</v>
+      </c>
+      <c r="D100" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100">
+        <v>2</v>
+      </c>
+      <c r="G100">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>50</v>
+      </c>
+      <c r="D102" t="s">
+        <v>43</v>
+      </c>
+      <c r="E102" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D103" t="s">
+        <v>43</v>
+      </c>
+      <c r="E103" t="s">
+        <v>39</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" t="s">
+        <v>50</v>
+      </c>
+      <c r="D104" t="s">
+        <v>43</v>
+      </c>
+      <c r="E104" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>50</v>
+      </c>
+      <c r="D105" t="s">
+        <v>43</v>
+      </c>
+      <c r="E105" t="s">
+        <v>37</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" t="s">
+        <v>50</v>
+      </c>
+      <c r="D106" t="s">
+        <v>43</v>
+      </c>
+      <c r="E106" t="s">
+        <v>39</v>
+      </c>
+      <c r="F106">
+        <v>4</v>
+      </c>
+      <c r="G106">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>5</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>50</v>
+      </c>
+      <c r="D107" t="s">
+        <v>44</v>
+      </c>
+      <c r="E107" t="s">
+        <v>36</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" t="s">
+        <v>50</v>
+      </c>
+      <c r="D108" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" t="s">
+        <v>50</v>
+      </c>
+      <c r="D109" t="s">
+        <v>44</v>
+      </c>
+      <c r="E109" t="s">
+        <v>38</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" t="s">
+        <v>44</v>
+      </c>
+      <c r="E110" t="s">
+        <v>36</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+      <c r="G110">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" t="s">
+        <v>50</v>
+      </c>
+      <c r="D111" t="s">
+        <v>44</v>
+      </c>
+      <c r="E111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>0.14285714285714279</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>50</v>
+      </c>
+      <c r="D112" t="s">
+        <v>44</v>
+      </c>
+      <c r="E112" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>0.14285714285714279</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>50</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>39</v>
+      </c>
+      <c r="F113">
+        <v>3</v>
+      </c>
+      <c r="G113">
+        <v>0.42857142857142849</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>50</v>
+      </c>
+      <c r="D114" t="s">
+        <v>45</v>
+      </c>
+      <c r="E114" t="s">
+        <v>35</v>
+      </c>
+      <c r="F114">
+        <v>2</v>
+      </c>
+      <c r="G114">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>5</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>50</v>
+      </c>
+      <c r="D115" t="s">
+        <v>45</v>
+      </c>
+      <c r="E115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" t="s">
+        <v>50</v>
+      </c>
+      <c r="D116" t="s">
+        <v>45</v>
+      </c>
+      <c r="E116" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>50</v>
+      </c>
+      <c r="D117" t="s">
+        <v>45</v>
+      </c>
+      <c r="E117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>50</v>
+      </c>
+      <c r="D118" t="s">
+        <v>45</v>
+      </c>
+      <c r="E118" t="s">
+        <v>39</v>
+      </c>
+      <c r="F118">
+        <v>3</v>
+      </c>
+      <c r="G118">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" t="s">
+        <v>45</v>
+      </c>
+      <c r="E119" t="s">
+        <v>36</v>
+      </c>
+      <c r="F119">
+        <v>3</v>
+      </c>
+      <c r="G119">
+        <v>0.23076923076923081</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" t="s">
+        <v>50</v>
+      </c>
+      <c r="D120" t="s">
+        <v>45</v>
+      </c>
+      <c r="E120" t="s">
+        <v>37</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120">
+        <v>0.38461538461538458</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>5</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>50</v>
+      </c>
+      <c r="D121" t="s">
+        <v>45</v>
+      </c>
+      <c r="E121" t="s">
+        <v>39</v>
+      </c>
+      <c r="F121">
+        <v>5</v>
+      </c>
+      <c r="G121">
+        <v>0.38461538461538458</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>51</v>
+      </c>
+      <c r="D122" t="s">
+        <v>43</v>
+      </c>
+      <c r="E122" t="s">
+        <v>36</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>51</v>
+      </c>
+      <c r="D123" t="s">
+        <v>43</v>
+      </c>
+      <c r="E123" t="s">
+        <v>39</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>51</v>
+      </c>
+      <c r="D124" t="s">
+        <v>44</v>
+      </c>
+      <c r="E124" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>5</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" t="s">
+        <v>51</v>
+      </c>
+      <c r="D125" t="s">
+        <v>44</v>
+      </c>
+      <c r="E125" t="s">
+        <v>36</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" t="s">
+        <v>51</v>
+      </c>
+      <c r="D126" t="s">
+        <v>44</v>
+      </c>
+      <c r="E126" t="s">
+        <v>37</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>51</v>
+      </c>
+      <c r="D127" t="s">
+        <v>45</v>
+      </c>
+      <c r="E127" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>5</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>51</v>
+      </c>
+      <c r="D128" t="s">
+        <v>45</v>
+      </c>
+      <c r="E128" t="s">
+        <v>39</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" t="s">
+        <v>51</v>
+      </c>
+      <c r="D129" t="s">
+        <v>45</v>
+      </c>
+      <c r="E129" t="s">
+        <v>35</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" t="s">
+        <v>45</v>
+      </c>
+      <c r="E130" t="s">
+        <v>36</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131" t="s">
+        <v>51</v>
+      </c>
+      <c r="D131" t="s">
+        <v>45</v>
+      </c>
+      <c r="E131" t="s">
+        <v>39</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>13</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>42</v>
+      </c>
+      <c r="D132" t="s">
+        <v>43</v>
+      </c>
+      <c r="E132" t="s">
+        <v>35</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>13</v>
+      </c>
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>42</v>
+      </c>
+      <c r="D133" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" t="s">
+        <v>36</v>
+      </c>
+      <c r="F133">
+        <v>6</v>
+      </c>
+      <c r="G133">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>13</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>42</v>
+      </c>
+      <c r="D134" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" t="s">
+        <v>38</v>
+      </c>
+      <c r="F134">
+        <v>3</v>
+      </c>
+      <c r="G134">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>13</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>42</v>
+      </c>
+      <c r="D135" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" t="s">
+        <v>39</v>
+      </c>
+      <c r="F135">
+        <v>7</v>
+      </c>
+      <c r="G135">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" t="s">
+        <v>42</v>
+      </c>
+      <c r="D136" t="s">
+        <v>43</v>
+      </c>
+      <c r="E136" t="s">
+        <v>35</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>13</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" t="s">
+        <v>42</v>
+      </c>
+      <c r="D137" t="s">
+        <v>43</v>
+      </c>
+      <c r="E137" t="s">
+        <v>36</v>
+      </c>
+      <c r="F137">
+        <v>2</v>
+      </c>
+      <c r="G137">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>13</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" t="s">
+        <v>43</v>
+      </c>
+      <c r="E138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>13</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" t="s">
+        <v>42</v>
+      </c>
+      <c r="D139" t="s">
+        <v>43</v>
+      </c>
+      <c r="E139" t="s">
+        <v>39</v>
+      </c>
+      <c r="F139">
+        <v>4</v>
+      </c>
+      <c r="G139">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" t="s">
+        <v>42</v>
+      </c>
+      <c r="D140" t="s">
+        <v>44</v>
+      </c>
+      <c r="E140" t="s">
+        <v>36</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>13</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>42</v>
+      </c>
+      <c r="D141" t="s">
+        <v>44</v>
+      </c>
+      <c r="E141" t="s">
+        <v>38</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>13</v>
+      </c>
+      <c r="B142" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>42</v>
+      </c>
+      <c r="D142" t="s">
+        <v>44</v>
+      </c>
+      <c r="E142" t="s">
+        <v>39</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>13</v>
+      </c>
+      <c r="B143" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" t="s">
+        <v>42</v>
+      </c>
+      <c r="D143" t="s">
+        <v>44</v>
+      </c>
+      <c r="E143" t="s">
+        <v>39</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>13</v>
+      </c>
+      <c r="B144" t="s">
+        <v>12</v>
+      </c>
+      <c r="C144" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" t="s">
+        <v>45</v>
+      </c>
+      <c r="E144" t="s">
+        <v>37</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>13</v>
+      </c>
+      <c r="B145" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" t="s">
+        <v>32</v>
+      </c>
+      <c r="D145" t="s">
+        <v>44</v>
+      </c>
+      <c r="E145" t="s">
+        <v>39</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+      <c r="B146" t="s">
+        <v>12</v>
+      </c>
+      <c r="C146" t="s">
+        <v>32</v>
+      </c>
+      <c r="D146" t="s">
+        <v>45</v>
+      </c>
+      <c r="E146" t="s">
+        <v>36</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>13</v>
+      </c>
+      <c r="B147" t="s">
+        <v>12</v>
+      </c>
+      <c r="C147" t="s">
+        <v>32</v>
+      </c>
+      <c r="D147" t="s">
+        <v>45</v>
+      </c>
+      <c r="E147" t="s">
+        <v>39</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>13</v>
+      </c>
+      <c r="B148" t="s">
+        <v>12</v>
+      </c>
+      <c r="C148" t="s">
+        <v>46</v>
+      </c>
+      <c r="D148" t="s">
+        <v>43</v>
+      </c>
+      <c r="E148" t="s">
+        <v>36</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>13</v>
+      </c>
+      <c r="B149" t="s">
+        <v>12</v>
+      </c>
+      <c r="C149" t="s">
+        <v>46</v>
+      </c>
+      <c r="D149" t="s">
+        <v>43</v>
+      </c>
+      <c r="E149" t="s">
+        <v>37</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>13</v>
+      </c>
+      <c r="B150" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" t="s">
+        <v>46</v>
+      </c>
+      <c r="D150" t="s">
+        <v>43</v>
+      </c>
+      <c r="E150" t="s">
+        <v>39</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>13</v>
+      </c>
+      <c r="B151" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" t="s">
+        <v>46</v>
+      </c>
+      <c r="D151" t="s">
+        <v>44</v>
+      </c>
+      <c r="E151" t="s">
+        <v>35</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>13</v>
+      </c>
+      <c r="B152" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" t="s">
+        <v>46</v>
+      </c>
+      <c r="D152" t="s">
+        <v>45</v>
+      </c>
+      <c r="E152" t="s">
+        <v>36</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>13</v>
+      </c>
+      <c r="B153" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>46</v>
+      </c>
+      <c r="D153" t="s">
+        <v>45</v>
+      </c>
+      <c r="E153" t="s">
+        <v>39</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>13</v>
+      </c>
+      <c r="B154" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" t="s">
+        <v>46</v>
+      </c>
+      <c r="D154" t="s">
+        <v>45</v>
+      </c>
+      <c r="E154" t="s">
+        <v>35</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>13</v>
+      </c>
+      <c r="B155" t="s">
+        <v>12</v>
+      </c>
+      <c r="C155" t="s">
+        <v>46</v>
+      </c>
+      <c r="D155" t="s">
+        <v>45</v>
+      </c>
+      <c r="E155" t="s">
+        <v>37</v>
+      </c>
+      <c r="F155">
+        <v>2</v>
+      </c>
+      <c r="G155">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>13</v>
+      </c>
+      <c r="B156" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" t="s">
+        <v>46</v>
+      </c>
+      <c r="D156" t="s">
+        <v>45</v>
+      </c>
+      <c r="E156" t="s">
+        <v>38</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>13</v>
+      </c>
+      <c r="B157" t="s">
+        <v>12</v>
+      </c>
+      <c r="C157" t="s">
+        <v>46</v>
+      </c>
+      <c r="D157" t="s">
+        <v>45</v>
+      </c>
+      <c r="E157" t="s">
+        <v>39</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" t="s">
+        <v>47</v>
+      </c>
+      <c r="D158" t="s">
+        <v>43</v>
+      </c>
+      <c r="E158" t="s">
+        <v>35</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>13</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" t="s">
+        <v>47</v>
+      </c>
+      <c r="D159" t="s">
+        <v>43</v>
+      </c>
+      <c r="E159" t="s">
+        <v>37</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>13</v>
+      </c>
+      <c r="B160" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" t="s">
+        <v>47</v>
+      </c>
+      <c r="D160" t="s">
+        <v>43</v>
+      </c>
+      <c r="E160" t="s">
+        <v>39</v>
+      </c>
+      <c r="F160">
+        <v>2</v>
+      </c>
+      <c r="G160">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>13</v>
+      </c>
+      <c r="B161" t="s">
+        <v>12</v>
+      </c>
+      <c r="C161" t="s">
+        <v>47</v>
+      </c>
+      <c r="D161" t="s">
+        <v>43</v>
+      </c>
+      <c r="E161" t="s">
+        <v>36</v>
+      </c>
+      <c r="F161">
+        <v>2</v>
+      </c>
+      <c r="G161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" t="s">
+        <v>47</v>
+      </c>
+      <c r="D162" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" t="s">
+        <v>39</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>13</v>
+      </c>
+      <c r="B163" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>47</v>
+      </c>
+      <c r="D163" t="s">
+        <v>44</v>
+      </c>
+      <c r="E163" t="s">
+        <v>36</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>13</v>
+      </c>
+      <c r="B164" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>47</v>
+      </c>
+      <c r="D164" t="s">
+        <v>44</v>
+      </c>
+      <c r="E164" t="s">
+        <v>38</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>13</v>
+      </c>
+      <c r="B165" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" t="s">
+        <v>47</v>
+      </c>
+      <c r="D165" t="s">
+        <v>44</v>
+      </c>
+      <c r="E165" t="s">
+        <v>39</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="B166" t="s">
+        <v>12</v>
+      </c>
+      <c r="C166" t="s">
+        <v>47</v>
+      </c>
+      <c r="D166" t="s">
+        <v>44</v>
+      </c>
+      <c r="E166" t="s">
+        <v>36</v>
+      </c>
+      <c r="F166">
+        <v>6</v>
+      </c>
+      <c r="G166">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>13</v>
+      </c>
+      <c r="B167" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" t="s">
+        <v>47</v>
+      </c>
+      <c r="D167" t="s">
+        <v>44</v>
+      </c>
+      <c r="E167" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167">
+        <v>3</v>
+      </c>
+      <c r="G167">
+        <v>0.14285714285714279</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>13</v>
+      </c>
+      <c r="B168" t="s">
+        <v>12</v>
+      </c>
+      <c r="C168" t="s">
+        <v>47</v>
+      </c>
+      <c r="D168" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168" t="s">
+        <v>39</v>
+      </c>
+      <c r="F168">
+        <v>12</v>
+      </c>
+      <c r="G168">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>13</v>
+      </c>
+      <c r="B169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" t="s">
+        <v>47</v>
+      </c>
+      <c r="D169" t="s">
+        <v>45</v>
+      </c>
+      <c r="E169" t="s">
+        <v>36</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>13</v>
+      </c>
+      <c r="B170" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" t="s">
+        <v>47</v>
+      </c>
+      <c r="D170" t="s">
+        <v>45</v>
+      </c>
+      <c r="E170" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>13</v>
+      </c>
+      <c r="B171" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" t="s">
+        <v>47</v>
+      </c>
+      <c r="D171" t="s">
+        <v>45</v>
+      </c>
+      <c r="E171" t="s">
+        <v>39</v>
+      </c>
+      <c r="F171">
+        <v>10</v>
+      </c>
+      <c r="G171">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>13</v>
+      </c>
+      <c r="B172" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" t="s">
+        <v>47</v>
+      </c>
+      <c r="D172" t="s">
+        <v>45</v>
+      </c>
+      <c r="E172" t="s">
+        <v>36</v>
+      </c>
+      <c r="F172">
+        <v>6</v>
+      </c>
+      <c r="G172">
+        <v>0.1764705882352941</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>13</v>
+      </c>
+      <c r="B173" t="s">
+        <v>12</v>
+      </c>
+      <c r="C173" t="s">
+        <v>47</v>
+      </c>
+      <c r="D173" t="s">
+        <v>45</v>
+      </c>
+      <c r="E173" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173">
+        <v>6</v>
+      </c>
+      <c r="G173">
+        <v>0.1764705882352941</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>13</v>
+      </c>
+      <c r="B174" t="s">
+        <v>12</v>
+      </c>
+      <c r="C174" t="s">
+        <v>47</v>
+      </c>
+      <c r="D174" t="s">
+        <v>45</v>
+      </c>
+      <c r="E174" t="s">
+        <v>38</v>
+      </c>
+      <c r="F174">
+        <v>4</v>
+      </c>
+      <c r="G174">
+        <v>0.1176470588235294</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>13</v>
+      </c>
+      <c r="B175" t="s">
+        <v>12</v>
+      </c>
+      <c r="C175" t="s">
+        <v>47</v>
+      </c>
+      <c r="D175" t="s">
+        <v>45</v>
+      </c>
+      <c r="E175" t="s">
+        <v>39</v>
+      </c>
+      <c r="F175">
+        <v>18</v>
+      </c>
+      <c r="G175">
+        <v>0.52941176470588236</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>13</v>
+      </c>
+      <c r="B176" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" t="s">
+        <v>48</v>
+      </c>
+      <c r="D176" t="s">
+        <v>43</v>
+      </c>
+      <c r="E176" t="s">
+        <v>35</v>
+      </c>
+      <c r="F176">
+        <v>4</v>
+      </c>
+      <c r="G176">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>13</v>
+      </c>
+      <c r="B177" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" t="s">
+        <v>48</v>
+      </c>
+      <c r="D177" t="s">
+        <v>43</v>
+      </c>
+      <c r="E177" t="s">
+        <v>36</v>
+      </c>
+      <c r="F177">
+        <v>12</v>
+      </c>
+      <c r="G177">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>13</v>
+      </c>
+      <c r="B178" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" t="s">
+        <v>48</v>
+      </c>
+      <c r="D178" t="s">
+        <v>43</v>
+      </c>
+      <c r="E178" t="s">
+        <v>37</v>
+      </c>
+      <c r="F178">
+        <v>2</v>
+      </c>
+      <c r="G178">
+        <v>4.1666666666666657E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>13</v>
+      </c>
+      <c r="B179" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" t="s">
+        <v>48</v>
+      </c>
+      <c r="D179" t="s">
+        <v>43</v>
+      </c>
+      <c r="E179" t="s">
+        <v>38</v>
+      </c>
+      <c r="F179">
+        <v>8</v>
+      </c>
+      <c r="G179">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>13</v>
+      </c>
+      <c r="B180" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" t="s">
+        <v>48</v>
+      </c>
+      <c r="D180" t="s">
+        <v>43</v>
+      </c>
+      <c r="E180" t="s">
+        <v>39</v>
+      </c>
+      <c r="F180">
+        <v>22</v>
+      </c>
+      <c r="G180">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>13</v>
+      </c>
+      <c r="B181" t="s">
+        <v>12</v>
+      </c>
+      <c r="C181" t="s">
+        <v>48</v>
+      </c>
+      <c r="D181" t="s">
+        <v>43</v>
+      </c>
+      <c r="E181" t="s">
+        <v>35</v>
+      </c>
+      <c r="F181">
+        <v>3</v>
+      </c>
+      <c r="G181">
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>13</v>
+      </c>
+      <c r="B182" t="s">
+        <v>12</v>
+      </c>
+      <c r="C182" t="s">
+        <v>48</v>
+      </c>
+      <c r="D182" t="s">
+        <v>43</v>
+      </c>
+      <c r="E182" t="s">
+        <v>36</v>
+      </c>
+      <c r="F182">
+        <v>10</v>
+      </c>
+      <c r="G182">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>13</v>
+      </c>
+      <c r="B183" t="s">
+        <v>12</v>
+      </c>
+      <c r="C183" t="s">
+        <v>48</v>
+      </c>
+      <c r="D183" t="s">
+        <v>43</v>
+      </c>
+      <c r="E183" t="s">
+        <v>37</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>13</v>
+      </c>
+      <c r="B184" t="s">
+        <v>12</v>
+      </c>
+      <c r="C184" t="s">
+        <v>48</v>
+      </c>
+      <c r="D184" t="s">
+        <v>43</v>
+      </c>
+      <c r="E184" t="s">
+        <v>38</v>
+      </c>
+      <c r="F184">
+        <v>4</v>
+      </c>
+      <c r="G184">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>13</v>
+      </c>
+      <c r="B185" t="s">
+        <v>12</v>
+      </c>
+      <c r="C185" t="s">
+        <v>48</v>
+      </c>
+      <c r="D185" t="s">
+        <v>43</v>
+      </c>
+      <c r="E185" t="s">
+        <v>39</v>
+      </c>
+      <c r="F185">
+        <v>14</v>
+      </c>
+      <c r="G185">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>13</v>
+      </c>
+      <c r="B186" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" t="s">
+        <v>48</v>
+      </c>
+      <c r="D186" t="s">
+        <v>44</v>
+      </c>
+      <c r="E186" t="s">
+        <v>35</v>
+      </c>
+      <c r="F186">
+        <v>4</v>
+      </c>
+      <c r="G186">
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>13</v>
+      </c>
+      <c r="B187" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" t="s">
+        <v>48</v>
+      </c>
+      <c r="D187" t="s">
+        <v>44</v>
+      </c>
+      <c r="E187" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187">
+        <v>14</v>
+      </c>
+      <c r="G187">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>13</v>
+      </c>
+      <c r="B188" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" t="s">
+        <v>48</v>
+      </c>
+      <c r="D188" t="s">
+        <v>44</v>
+      </c>
+      <c r="E188" t="s">
+        <v>38</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>2.3809523809523812E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>13</v>
+      </c>
+      <c r="B189" t="s">
+        <v>6</v>
+      </c>
+      <c r="C189" t="s">
+        <v>48</v>
+      </c>
+      <c r="D189" t="s">
+        <v>44</v>
+      </c>
+      <c r="E189" t="s">
+        <v>39</v>
+      </c>
+      <c r="F189">
+        <v>23</v>
+      </c>
+      <c r="G189">
+        <v>0.54761904761904767</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>13</v>
+      </c>
+      <c r="B190" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" t="s">
+        <v>48</v>
+      </c>
+      <c r="D190" t="s">
+        <v>44</v>
+      </c>
+      <c r="E190" t="s">
+        <v>35</v>
+      </c>
+      <c r="F190">
+        <v>5</v>
+      </c>
+      <c r="G190">
+        <v>0.12195121951219511</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>13</v>
+      </c>
+      <c r="B191" t="s">
+        <v>12</v>
+      </c>
+      <c r="C191" t="s">
+        <v>48</v>
+      </c>
+      <c r="D191" t="s">
+        <v>44</v>
+      </c>
+      <c r="E191" t="s">
+        <v>36</v>
+      </c>
+      <c r="F191">
+        <v>11</v>
+      </c>
+      <c r="G191">
+        <v>0.26829268292682928</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>13</v>
+      </c>
+      <c r="B192" t="s">
+        <v>12</v>
+      </c>
+      <c r="C192" t="s">
+        <v>48</v>
+      </c>
+      <c r="D192" t="s">
+        <v>44</v>
+      </c>
+      <c r="E192" t="s">
+        <v>39</v>
+      </c>
+      <c r="F192">
+        <v>25</v>
+      </c>
+      <c r="G192">
+        <v>0.6097560975609756</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>13</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" t="s">
+        <v>48</v>
+      </c>
+      <c r="D193" t="s">
+        <v>45</v>
+      </c>
+      <c r="E193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F193">
+        <v>3</v>
+      </c>
+      <c r="G193">
+        <v>0.13636363636363641</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>13</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" t="s">
+        <v>48</v>
+      </c>
+      <c r="D194" t="s">
+        <v>45</v>
+      </c>
+      <c r="E194" t="s">
+        <v>36</v>
+      </c>
+      <c r="F194">
+        <v>6</v>
+      </c>
+      <c r="G194">
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>13</v>
+      </c>
+      <c r="B195" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" t="s">
+        <v>48</v>
+      </c>
+      <c r="D195" t="s">
+        <v>45</v>
+      </c>
+      <c r="E195" t="s">
+        <v>37</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195">
+        <v>4.5454545454545463E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>13</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" t="s">
+        <v>48</v>
+      </c>
+      <c r="D196" t="s">
+        <v>45</v>
+      </c>
+      <c r="E196" t="s">
+        <v>38</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>4.5454545454545463E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>13</v>
+      </c>
+      <c r="B197" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" t="s">
+        <v>48</v>
+      </c>
+      <c r="D197" t="s">
+        <v>45</v>
+      </c>
+      <c r="E197" t="s">
+        <v>39</v>
+      </c>
+      <c r="F197">
+        <v>11</v>
+      </c>
+      <c r="G197">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>13</v>
+      </c>
+      <c r="B198" t="s">
+        <v>12</v>
+      </c>
+      <c r="C198" t="s">
+        <v>48</v>
+      </c>
+      <c r="D198" t="s">
+        <v>45</v>
+      </c>
+      <c r="E198" t="s">
+        <v>36</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+      <c r="G198">
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>13</v>
+      </c>
+      <c r="B199" t="s">
+        <v>12</v>
+      </c>
+      <c r="C199" t="s">
+        <v>48</v>
+      </c>
+      <c r="D199" t="s">
+        <v>45</v>
+      </c>
+      <c r="E199" t="s">
+        <v>37</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>13</v>
+      </c>
+      <c r="B200" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" t="s">
+        <v>48</v>
+      </c>
+      <c r="D200" t="s">
+        <v>45</v>
+      </c>
+      <c r="E200" t="s">
+        <v>39</v>
+      </c>
+      <c r="F200">
+        <v>6</v>
+      </c>
+      <c r="G200">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>13</v>
+      </c>
+      <c r="B201" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" t="s">
+        <v>49</v>
+      </c>
+      <c r="D201" t="s">
+        <v>43</v>
+      </c>
+      <c r="E201" t="s">
+        <v>38</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>13</v>
+      </c>
+      <c r="B202" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" t="s">
+        <v>49</v>
+      </c>
+      <c r="D202" t="s">
+        <v>43</v>
+      </c>
+      <c r="E202" t="s">
+        <v>39</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>13</v>
+      </c>
+      <c r="B203" t="s">
+        <v>12</v>
+      </c>
+      <c r="C203" t="s">
+        <v>49</v>
+      </c>
+      <c r="D203" t="s">
+        <v>43</v>
+      </c>
+      <c r="E203" t="s">
+        <v>36</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>13</v>
+      </c>
+      <c r="B204" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204" t="s">
+        <v>49</v>
+      </c>
+      <c r="D204" t="s">
+        <v>43</v>
+      </c>
+      <c r="E204" t="s">
+        <v>37</v>
+      </c>
+      <c r="F204">
+        <v>3</v>
+      </c>
+      <c r="G204">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>13</v>
+      </c>
+      <c r="B205" t="s">
+        <v>12</v>
+      </c>
+      <c r="C205" t="s">
+        <v>49</v>
+      </c>
+      <c r="D205" t="s">
+        <v>44</v>
+      </c>
+      <c r="E205" t="s">
+        <v>39</v>
+      </c>
+      <c r="F205">
+        <v>4</v>
+      </c>
+      <c r="G205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>13</v>
+      </c>
+      <c r="B206" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" t="s">
+        <v>49</v>
+      </c>
+      <c r="D206" t="s">
+        <v>45</v>
+      </c>
+      <c r="E206" t="s">
+        <v>36</v>
+      </c>
+      <c r="F206">
+        <v>2</v>
+      </c>
+      <c r="G206">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>13</v>
+      </c>
+      <c r="B207" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" t="s">
+        <v>49</v>
+      </c>
+      <c r="D207" t="s">
+        <v>45</v>
+      </c>
+      <c r="E207" t="s">
+        <v>37</v>
+      </c>
+      <c r="F207">
+        <v>2</v>
+      </c>
+      <c r="G207">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>13</v>
+      </c>
+      <c r="B208" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208" t="s">
+        <v>49</v>
+      </c>
+      <c r="D208" t="s">
+        <v>45</v>
+      </c>
+      <c r="E208" t="s">
+        <v>38</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>13</v>
+      </c>
+      <c r="B209" t="s">
+        <v>12</v>
+      </c>
+      <c r="C209" t="s">
+        <v>49</v>
+      </c>
+      <c r="D209" t="s">
+        <v>45</v>
+      </c>
+      <c r="E209" t="s">
+        <v>37</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>13</v>
+      </c>
+      <c r="B210" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" t="s">
+        <v>50</v>
+      </c>
+      <c r="D210" t="s">
+        <v>43</v>
+      </c>
+      <c r="E210" t="s">
+        <v>36</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>13</v>
+      </c>
+      <c r="B211" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" t="s">
+        <v>50</v>
+      </c>
+      <c r="D211" t="s">
+        <v>43</v>
+      </c>
+      <c r="E211" t="s">
+        <v>38</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>13</v>
+      </c>
+      <c r="B212" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" t="s">
+        <v>50</v>
+      </c>
+      <c r="D212" t="s">
+        <v>43</v>
+      </c>
+      <c r="E212" t="s">
+        <v>39</v>
+      </c>
+      <c r="F212">
+        <v>2</v>
+      </c>
+      <c r="G212">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>13</v>
+      </c>
+      <c r="B213" t="s">
+        <v>12</v>
+      </c>
+      <c r="C213" t="s">
+        <v>50</v>
+      </c>
+      <c r="D213" t="s">
+        <v>43</v>
+      </c>
+      <c r="E213" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>13</v>
+      </c>
+      <c r="B214" t="s">
+        <v>12</v>
+      </c>
+      <c r="C214" t="s">
+        <v>50</v>
+      </c>
+      <c r="D214" t="s">
+        <v>43</v>
+      </c>
+      <c r="E214" t="s">
+        <v>37</v>
+      </c>
+      <c r="F214">
+        <v>5</v>
+      </c>
+      <c r="G214">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>13</v>
+      </c>
+      <c r="B215" t="s">
+        <v>12</v>
+      </c>
+      <c r="C215" t="s">
+        <v>50</v>
+      </c>
+      <c r="D215" t="s">
+        <v>43</v>
+      </c>
+      <c r="E215" t="s">
+        <v>39</v>
+      </c>
+      <c r="F215">
+        <v>4</v>
+      </c>
+      <c r="G215">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>13</v>
+      </c>
+      <c r="B216" t="s">
+        <v>6</v>
+      </c>
+      <c r="C216" t="s">
+        <v>50</v>
+      </c>
+      <c r="D216" t="s">
+        <v>44</v>
+      </c>
+      <c r="E216" t="s">
+        <v>39</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>13</v>
+      </c>
+      <c r="B217" t="s">
+        <v>12</v>
+      </c>
+      <c r="C217" t="s">
+        <v>50</v>
+      </c>
+      <c r="D217" t="s">
+        <v>44</v>
+      </c>
+      <c r="E217" t="s">
+        <v>35</v>
+      </c>
+      <c r="F217">
+        <v>2</v>
+      </c>
+      <c r="G217">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>13</v>
+      </c>
+      <c r="B218" t="s">
+        <v>12</v>
+      </c>
+      <c r="C218" t="s">
+        <v>50</v>
+      </c>
+      <c r="D218" t="s">
+        <v>44</v>
+      </c>
+      <c r="E218" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>13</v>
+      </c>
+      <c r="B219" t="s">
+        <v>12</v>
+      </c>
+      <c r="C219" t="s">
+        <v>50</v>
+      </c>
+      <c r="D219" t="s">
+        <v>44</v>
+      </c>
+      <c r="E219" t="s">
+        <v>37</v>
+      </c>
+      <c r="F219">
+        <v>2</v>
+      </c>
+      <c r="G219">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>13</v>
+      </c>
+      <c r="B220" t="s">
+        <v>12</v>
+      </c>
+      <c r="C220" t="s">
+        <v>50</v>
+      </c>
+      <c r="D220" t="s">
+        <v>44</v>
+      </c>
+      <c r="E220" t="s">
+        <v>39</v>
+      </c>
+      <c r="F220">
+        <v>3</v>
+      </c>
+      <c r="G220">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>13</v>
+      </c>
+      <c r="B221" t="s">
+        <v>6</v>
+      </c>
+      <c r="C221" t="s">
+        <v>50</v>
+      </c>
+      <c r="D221" t="s">
+        <v>45</v>
+      </c>
+      <c r="E221" t="s">
+        <v>36</v>
+      </c>
+      <c r="F221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>13</v>
+      </c>
+      <c r="B222" t="s">
+        <v>6</v>
+      </c>
+      <c r="C222" t="s">
+        <v>50</v>
+      </c>
+      <c r="D222" t="s">
+        <v>45</v>
+      </c>
+      <c r="E222" t="s">
+        <v>37</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>13</v>
+      </c>
+      <c r="B223" t="s">
+        <v>6</v>
+      </c>
+      <c r="C223" t="s">
+        <v>50</v>
+      </c>
+      <c r="D223" t="s">
+        <v>45</v>
+      </c>
+      <c r="E223" t="s">
+        <v>38</v>
+      </c>
+      <c r="F223">
+        <v>2</v>
+      </c>
+      <c r="G223">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>13</v>
+      </c>
+      <c r="B224" t="s">
+        <v>6</v>
+      </c>
+      <c r="C224" t="s">
+        <v>50</v>
+      </c>
+      <c r="D224" t="s">
+        <v>45</v>
+      </c>
+      <c r="E224" t="s">
+        <v>39</v>
+      </c>
+      <c r="F224">
+        <v>5</v>
+      </c>
+      <c r="G224">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>13</v>
+      </c>
+      <c r="B225" t="s">
+        <v>12</v>
+      </c>
+      <c r="C225" t="s">
+        <v>50</v>
+      </c>
+      <c r="D225" t="s">
+        <v>45</v>
+      </c>
+      <c r="E225" t="s">
+        <v>36</v>
+      </c>
+      <c r="F225">
+        <v>2</v>
+      </c>
+      <c r="G225">
+        <v>0.16666666666666671</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>13</v>
+      </c>
+      <c r="B226" t="s">
+        <v>12</v>
+      </c>
+      <c r="C226" t="s">
+        <v>50</v>
+      </c>
+      <c r="D226" t="s">
+        <v>45</v>
+      </c>
+      <c r="E226" t="s">
+        <v>37</v>
+      </c>
+      <c r="F226">
+        <v>6</v>
+      </c>
+      <c r="G226">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>13</v>
+      </c>
+      <c r="B227" t="s">
+        <v>12</v>
+      </c>
+      <c r="C227" t="s">
+        <v>50</v>
+      </c>
+      <c r="D227" t="s">
+        <v>45</v>
+      </c>
+      <c r="E227" t="s">
+        <v>39</v>
+      </c>
+      <c r="F227">
+        <v>4</v>
+      </c>
+      <c r="G227">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>13</v>
+      </c>
+      <c r="B228" t="s">
+        <v>6</v>
+      </c>
+      <c r="C228" t="s">
+        <v>51</v>
+      </c>
+      <c r="D228" t="s">
+        <v>43</v>
+      </c>
+      <c r="E228" t="s">
+        <v>36</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>13</v>
+      </c>
+      <c r="B229" t="s">
+        <v>6</v>
+      </c>
+      <c r="C229" t="s">
+        <v>51</v>
+      </c>
+      <c r="D229" t="s">
+        <v>43</v>
+      </c>
+      <c r="E229" t="s">
+        <v>38</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+      <c r="G229">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>13</v>
+      </c>
+      <c r="B230" t="s">
+        <v>6</v>
+      </c>
+      <c r="C230" t="s">
+        <v>51</v>
+      </c>
+      <c r="D230" t="s">
+        <v>43</v>
+      </c>
+      <c r="E230" t="s">
+        <v>39</v>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="G230">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>13</v>
+      </c>
+      <c r="B231" t="s">
+        <v>12</v>
+      </c>
+      <c r="C231" t="s">
+        <v>51</v>
+      </c>
+      <c r="D231" t="s">
+        <v>43</v>
+      </c>
+      <c r="E231" t="s">
+        <v>36</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="G231">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>13</v>
+      </c>
+      <c r="B232" t="s">
+        <v>12</v>
+      </c>
+      <c r="C232" t="s">
+        <v>51</v>
+      </c>
+      <c r="D232" t="s">
+        <v>43</v>
+      </c>
+      <c r="E232" t="s">
+        <v>39</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>13</v>
+      </c>
+      <c r="B233" t="s">
+        <v>6</v>
+      </c>
+      <c r="C233" t="s">
+        <v>51</v>
+      </c>
+      <c r="D233" t="s">
+        <v>44</v>
+      </c>
+      <c r="E233" t="s">
+        <v>37</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>13</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234" t="s">
+        <v>51</v>
+      </c>
+      <c r="D234" t="s">
+        <v>44</v>
+      </c>
+      <c r="E234" t="s">
+        <v>39</v>
+      </c>
+      <c r="F234">
+        <v>1</v>
+      </c>
+      <c r="G234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>13</v>
+      </c>
+      <c r="B235" t="s">
+        <v>6</v>
+      </c>
+      <c r="C235" t="s">
+        <v>51</v>
+      </c>
+      <c r="D235" t="s">
+        <v>45</v>
+      </c>
+      <c r="E235" t="s">
+        <v>38</v>
+      </c>
+      <c r="F235">
+        <v>1</v>
+      </c>
+      <c r="G235">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>13</v>
+      </c>
+      <c r="B236" t="s">
+        <v>6</v>
+      </c>
+      <c r="C236" t="s">
+        <v>51</v>
+      </c>
+      <c r="D236" t="s">
+        <v>45</v>
+      </c>
+      <c r="E236" t="s">
+        <v>39</v>
+      </c>
+      <c r="F236">
+        <v>2</v>
+      </c>
+      <c r="G236">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>13</v>
+      </c>
+      <c r="B237" t="s">
+        <v>12</v>
+      </c>
+      <c r="C237" t="s">
+        <v>51</v>
+      </c>
+      <c r="D237" t="s">
+        <v>45</v>
+      </c>
+      <c r="E237" t="s">
+        <v>37</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+      <c r="G237">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>13</v>
+      </c>
+      <c r="B238" t="s">
+        <v>12</v>
+      </c>
+      <c r="C238" t="s">
+        <v>51</v>
+      </c>
+      <c r="D238" t="s">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>39</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+      <c r="G238">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G238" xr:uid="{00000000-0001-0000-0400-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Hombre"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Salud"/>
+        <filter val="Viajes de cuidado"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C350AF-BA23-46BD-A07F-44907F281328}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="39.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>212</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2">
+        <v>40</v>
+      </c>
+      <c r="D2" s="4">
+        <f>C2/A2</f>
+        <v>0.18867924528301888</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>218</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2">
+        <v>36</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D5" si="0">C3/A3</f>
+        <v>0.16513761467889909</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>221</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2">
+        <v>79</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.3574660633484163</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>210</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="2">
+        <v>89</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.4238095238095238</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>